--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Brzozowa_9_Poznan_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Brzozowa_9_Poznan_NK38.xlsx
@@ -168,10 +168,10 @@
     <t>ul. Brzozowa 9, Poznań</t>
   </si>
   <si>
-    <t>21.10.2026, 17:30</t>
-  </si>
-  <si>
-    <t>Wygenerowano 27.10.2026, 17:30:55 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 10:10</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 10:10:16 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Brzozowa_9_Poznan_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Brzozowa_9_Poznan_NK38.xlsx
@@ -4,158 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Podsumowanie" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Obliczenia i cennik" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Kalkulacja" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="E55" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B56" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E56" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B57" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E57" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E58" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E59" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E60" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E61" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E62" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B63" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E63" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B64" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E64" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B65" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E65" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B66" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E66" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B67" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E67" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B68" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E68" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B69" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E69" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B70" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E70" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B71" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E71" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E72" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B73" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E73" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B74" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E74" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B75" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E75" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B76" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E76" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B77" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E77" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B78" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E78" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B79" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E79" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="E80" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B81" authorId="0">
-      <text/>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="236">
   <si>
@@ -168,10 +22,10 @@
     <t>ul. Brzozowa 9, Poznań</t>
   </si>
   <si>
-    <t>21.10.2026, 10:10</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 10:10:16 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 10:28</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 10:28:00 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena</t>
@@ -393,6 +247,270 @@
     <t>60 zł / MP / mies.</t>
   </si>
   <si>
+    <t>Koszty · 2000 kg · 14%</t>
+  </si>
+  <si>
+    <t>Skąd się biorą kwoty (wariant 2000 kg) · ceny netto w zł</t>
+  </si>
+  <si>
+    <t>Materiały i urządzenia</t>
+  </si>
+  <si>
+    <t>Cena platformy D / S / N.P.</t>
+  </si>
+  <si>
+    <t>32 500 zł / 19 825 zł / 27 625 zł</t>
+  </si>
+  <si>
+    <t>Platformy S z dopłatami</t>
+  </si>
+  <si>
+    <t>79 300 zł</t>
+  </si>
+  <si>
+    <t>Platformy D z dopłatami</t>
+  </si>
+  <si>
+    <t>195 000 zł</t>
+  </si>
+  <si>
+    <t>Platformy N.P.</t>
+  </si>
+  <si>
+    <t>0 zł</t>
+  </si>
+  <si>
+    <t>Siłowniki (pary): std / 2000 / 2250</t>
+  </si>
+  <si>
+    <t>10 / 0 / 0</t>
+  </si>
+  <si>
+    <t>Hydraulika</t>
+  </si>
+  <si>
+    <t>43 830 zł</t>
+  </si>
+  <si>
+    <t>Barierki i maskownice</t>
+  </si>
+  <si>
+    <t>3600 zł</t>
+  </si>
+  <si>
+    <t>Elektryka</t>
+  </si>
+  <si>
+    <t>5640 zł</t>
+  </si>
+  <si>
+    <t>Mechanika zakupowa i pozostałe</t>
+  </si>
+  <si>
+    <t>32 303 zł</t>
+  </si>
+  <si>
+    <t>Suma Q=2000</t>
+  </si>
+  <si>
+    <t>359 673 zł</t>
+  </si>
+  <si>
+    <t>Suma Q=2500 (+7%)</t>
+  </si>
+  <si>
+    <t>384 850 zł</t>
+  </si>
+  <si>
+    <t>Platformy NK41: 12 × 12000 zł</t>
+  </si>
+  <si>
+    <t>144 000 zł</t>
+  </si>
+  <si>
+    <t>Hydraulika (siłownik 850 + rury i złączki 470 + wąż 100)</t>
+  </si>
+  <si>
+    <t>17 040 zł</t>
+  </si>
+  <si>
+    <t>Agregat hydrauliczny</t>
+  </si>
+  <si>
+    <t>10 121 zł</t>
+  </si>
+  <si>
+    <t>Sterowanie i elektryka: na agregat</t>
+  </si>
+  <si>
+    <t>4200 zł</t>
+  </si>
+  <si>
+    <t>Sterowanie i elektryka: na urządzenie</t>
+  </si>
+  <si>
+    <t>6000 zł</t>
+  </si>
+  <si>
+    <t>Suma 2000 kg</t>
+  </si>
+  <si>
+    <t>181 361 zł</t>
+  </si>
+  <si>
+    <t>Suma 2500 kg (nie wpisano dopłaty)</t>
+  </si>
+  <si>
+    <t>Montaż, narzuty i cena</t>
+  </si>
+  <si>
+    <t>Pozycja</t>
+  </si>
+  <si>
+    <t>Skąd ta kwota</t>
+  </si>
+  <si>
+    <t>Kwota</t>
+  </si>
+  <si>
+    <t>Osobodni montażu</t>
+  </si>
+  <si>
+    <t>z cennika osobodni na urządzenie + utrudnienia (obie pozycje)</t>
+  </si>
+  <si>
+    <t>Tygodnie / dni montażu</t>
+  </si>
+  <si>
+    <t>tygodniowe wyjazdy ekipy</t>
+  </si>
+  <si>
+    <t>Osobodni podróży i rozładunku</t>
+  </si>
+  <si>
+    <t>pomiary, odbiory, rozładunek i dojazdy ekipy</t>
+  </si>
+  <si>
+    <t>Dni pracy ekipy</t>
+  </si>
+  <si>
+    <t>(osd montażu + podróży) ÷ 4 os.</t>
+  </si>
+  <si>
+    <t>Kilometry auta</t>
+  </si>
+  <si>
+    <t>dojazdy na montaż, pomiary i odbiory w obie strony</t>
+  </si>
+  <si>
+    <t>Noclegi (osobonoce)</t>
+  </si>
+  <si>
+    <t>(dni pracy + 1) × 4 os.</t>
+  </si>
+  <si>
+    <t>Urządzenia</t>
+  </si>
+  <si>
+    <t>obie pozycje (patrz wyżej)</t>
+  </si>
+  <si>
+    <t>Paliwo</t>
+  </si>
+  <si>
+    <t>8980 km × 113 zł/100 km (12 l × 9,4 zł)</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>144 noclegów × 130 zł/doba</t>
+  </si>
+  <si>
+    <t>2 TIR × 4500 zł</t>
+  </si>
+  <si>
+    <t>Spider Crane</t>
+  </si>
+  <si>
+    <t>3 dni × 2400 zł/dzień</t>
+  </si>
+  <si>
+    <t>Rozładunek, sprzęt</t>
+  </si>
+  <si>
+    <t>2000 zł jednorazowo</t>
+  </si>
+  <si>
+    <t>Rozładunek, ludzie</t>
+  </si>
+  <si>
+    <t>1 dni × 4 os. × 400 zł</t>
+  </si>
+  <si>
+    <t>Dojazdy, ludzie</t>
+  </si>
+  <si>
+    <t>40,54 osd podróży × 400 zł</t>
+  </si>
+  <si>
+    <t>93,4 osd × 400 zł (średnia stawka)</t>
+  </si>
+  <si>
+    <t>Diety</t>
+  </si>
+  <si>
+    <t>137,94 osd × 45 zł</t>
+  </si>
+  <si>
+    <t>Suma przed narzutami</t>
+  </si>
+  <si>
+    <t>suma kosztów powyżej</t>
+  </si>
+  <si>
+    <t>KOB</t>
+  </si>
+  <si>
+    <t>0,515% ceny przed podatkiem (784 401 zł)</t>
+  </si>
+  <si>
+    <t>GDW</t>
+  </si>
+  <si>
+    <t>2,685% ceny przed podatkiem</t>
+  </si>
+  <si>
+    <t>Zysk 14%</t>
+  </si>
+  <si>
+    <t>14% ceny przed podatkiem</t>
+  </si>
+  <si>
+    <t>Zysk z narzutem (zysk + GDW)</t>
+  </si>
+  <si>
+    <t>zysk 14% + GDW 2,685%</t>
+  </si>
+  <si>
+    <t>Podatek</t>
+  </si>
+  <si>
+    <t>14% od robocizny (61 384 zł) i zysku z narzutem</t>
+  </si>
+  <si>
+    <t>Cena kontraktu, zysk 14%</t>
+  </si>
+  <si>
+    <t>suma ÷ (1 − KOB − GDW − zysk) + podatek</t>
+  </si>
+  <si>
+    <t>Koszt rzeczywisty</t>
+  </si>
+  <si>
+    <t>cena − zysk z narzutem</t>
+  </si>
+  <si>
     <t>Pozostałe dane wejściowe</t>
   </si>
   <si>
@@ -430,270 +548,6 @@
   </si>
   <si>
     <t>4.325</t>
-  </si>
-  <si>
-    <t>Koszty · 2000 kg · 14%</t>
-  </si>
-  <si>
-    <t>Strona 1: obliczenia · strona 2: cennik szablonu NK38</t>
-  </si>
-  <si>
-    <t>Materiały i urządzenia</t>
-  </si>
-  <si>
-    <t>Cena platformy D / S / N.P.</t>
-  </si>
-  <si>
-    <t>32 500 zł / 19 825 zł / 27 625 zł</t>
-  </si>
-  <si>
-    <t>Platformy S z dopłatami</t>
-  </si>
-  <si>
-    <t>79 300 zł</t>
-  </si>
-  <si>
-    <t>Platformy D z dopłatami</t>
-  </si>
-  <si>
-    <t>195 000 zł</t>
-  </si>
-  <si>
-    <t>Platformy N.P.</t>
-  </si>
-  <si>
-    <t>0 zł</t>
-  </si>
-  <si>
-    <t>Siłowniki (pary): std / 2000 / 2250</t>
-  </si>
-  <si>
-    <t>10 / 0 / 0</t>
-  </si>
-  <si>
-    <t>Hydraulika</t>
-  </si>
-  <si>
-    <t>43 830 zł</t>
-  </si>
-  <si>
-    <t>Barierki i maskownice</t>
-  </si>
-  <si>
-    <t>3600 zł</t>
-  </si>
-  <si>
-    <t>Elektryka</t>
-  </si>
-  <si>
-    <t>5640 zł</t>
-  </si>
-  <si>
-    <t>Mechanika zakupowa i pozostałe</t>
-  </si>
-  <si>
-    <t>32 303 zł</t>
-  </si>
-  <si>
-    <t>Suma Q=2000</t>
-  </si>
-  <si>
-    <t>359 673 zł</t>
-  </si>
-  <si>
-    <t>Suma Q=2500 (+7%)</t>
-  </si>
-  <si>
-    <t>384 850 zł</t>
-  </si>
-  <si>
-    <t>Platformy NK41: 12 × 12000 zł</t>
-  </si>
-  <si>
-    <t>144 000 zł</t>
-  </si>
-  <si>
-    <t>Hydraulika (siłownik 850 + rury i złączki 470 + wąż 100)</t>
-  </si>
-  <si>
-    <t>17 040 zł</t>
-  </si>
-  <si>
-    <t>Agregat hydrauliczny</t>
-  </si>
-  <si>
-    <t>10 121 zł</t>
-  </si>
-  <si>
-    <t>Sterowanie i elektryka: na agregat</t>
-  </si>
-  <si>
-    <t>4200 zł</t>
-  </si>
-  <si>
-    <t>Sterowanie i elektryka: na urządzenie</t>
-  </si>
-  <si>
-    <t>6000 zł</t>
-  </si>
-  <si>
-    <t>Suma 2000 kg</t>
-  </si>
-  <si>
-    <t>181 361 zł</t>
-  </si>
-  <si>
-    <t>Suma 2500 kg (nie wpisano dopłaty)</t>
-  </si>
-  <si>
-    <t>Montaż, narzuty i cena</t>
-  </si>
-  <si>
-    <t>Pozycja</t>
-  </si>
-  <si>
-    <t>Skąd ta kwota</t>
-  </si>
-  <si>
-    <t>Kwota</t>
-  </si>
-  <si>
-    <t>Osobodni montażu</t>
-  </si>
-  <si>
-    <t>z cennika osobodni na urządzenie + utrudnienia (obie pozycje)</t>
-  </si>
-  <si>
-    <t>Tygodnie / dni montażu</t>
-  </si>
-  <si>
-    <t>tygodniowe wyjazdy ekipy</t>
-  </si>
-  <si>
-    <t>Osobodni podróży i rozładunku</t>
-  </si>
-  <si>
-    <t>pomiary, odbiory, rozładunek i dojazdy ekipy</t>
-  </si>
-  <si>
-    <t>Dni pracy ekipy</t>
-  </si>
-  <si>
-    <t>(osd montażu + podróży) ÷ 4 os.</t>
-  </si>
-  <si>
-    <t>Kilometry auta</t>
-  </si>
-  <si>
-    <t>dojazdy na montaż, pomiary i odbiory w obie strony</t>
-  </si>
-  <si>
-    <t>Noclegi (osobonoce)</t>
-  </si>
-  <si>
-    <t>(dni pracy + 1) × 4 os.</t>
-  </si>
-  <si>
-    <t>Urządzenia</t>
-  </si>
-  <si>
-    <t>obie pozycje (patrz wyżej)</t>
-  </si>
-  <si>
-    <t>Paliwo</t>
-  </si>
-  <si>
-    <t>8980 km × 113 zł/100 km (12 l × 9,4 zł)</t>
-  </si>
-  <si>
-    <t>Hotel</t>
-  </si>
-  <si>
-    <t>144 noclegów × 130 zł/doba</t>
-  </si>
-  <si>
-    <t>2 TIR × 4500 zł</t>
-  </si>
-  <si>
-    <t>Spider Crane</t>
-  </si>
-  <si>
-    <t>3 dni × 2400 zł/dzień</t>
-  </si>
-  <si>
-    <t>Rozładunek, sprzęt</t>
-  </si>
-  <si>
-    <t>2000 zł jednorazowo</t>
-  </si>
-  <si>
-    <t>Rozładunek, ludzie</t>
-  </si>
-  <si>
-    <t>1 dni × 4 os. × 400 zł</t>
-  </si>
-  <si>
-    <t>Dojazdy, ludzie</t>
-  </si>
-  <si>
-    <t>40,54 osd podróży × 400 zł</t>
-  </si>
-  <si>
-    <t>93,4 osd × 400 zł (średnia stawka)</t>
-  </si>
-  <si>
-    <t>Diety</t>
-  </si>
-  <si>
-    <t>137,94 osd × 45 zł</t>
-  </si>
-  <si>
-    <t>Suma przed narzutami</t>
-  </si>
-  <si>
-    <t>suma kosztów powyżej</t>
-  </si>
-  <si>
-    <t>KOB</t>
-  </si>
-  <si>
-    <t>0,515% ceny przed podatkiem (784 401 zł)</t>
-  </si>
-  <si>
-    <t>GDW</t>
-  </si>
-  <si>
-    <t>2,685% ceny przed podatkiem</t>
-  </si>
-  <si>
-    <t>Zysk 14%</t>
-  </si>
-  <si>
-    <t>14% ceny przed podatkiem</t>
-  </si>
-  <si>
-    <t>Zysk z narzutem (zysk + GDW)</t>
-  </si>
-  <si>
-    <t>zysk 14% + GDW 2,685%</t>
-  </si>
-  <si>
-    <t>Podatek</t>
-  </si>
-  <si>
-    <t>14% od robocizny (61 384 zł) i zysku z narzutem</t>
-  </si>
-  <si>
-    <t>Cena kontraktu, zysk 14%</t>
-  </si>
-  <si>
-    <t>suma ÷ (1 − KOB − GDW − zysk) + podatek</t>
-  </si>
-  <si>
-    <t>Koszt rzeczywisty</t>
-  </si>
-  <si>
-    <t>cena − zysk z narzutem</t>
   </si>
   <si>
     <t>Cennik szablonu NK38</t>
@@ -1091,7 +945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -1217,17 +1071,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
@@ -1268,10 +1122,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
+      <alignment indent="3"/>
     </xf>
     <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1615,7 +1472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2362,90 +2219,1172 @@
         <v>15840</v>
       </c>
     </row>
-    <row r="58" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
+    <row r="58" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="43" t="s">
+      <c r="A59" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="B59" s="44" t="s">
-        <v>80</v>
-      </c>
+      <c r="B59" s="44"/>
       <c r="C59" s="44"/>
       <c r="D59" s="44"/>
       <c r="E59" s="44"/>
       <c r="F59" s="44"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="43" t="s">
+    <row r="61" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" s="45"/>
+      <c r="C62" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="D62" s="46"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="46"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="B60" s="44" t="s">
+      <c r="B63" s="45"/>
+      <c r="C63" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="C60" s="44"/>
-      <c r="D60" s="44"/>
-      <c r="E60" s="44"/>
-      <c r="F60" s="44"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="43" t="s">
+      <c r="D63" s="46"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="46"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="B61" s="44" t="s">
+      <c r="B64" s="45"/>
+      <c r="C64" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="C61" s="44"/>
-      <c r="D61" s="44"/>
-      <c r="E61" s="44"/>
-      <c r="F61" s="44"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="43" t="s">
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="46"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="B62" s="44" t="s">
+      <c r="B65" s="45"/>
+      <c r="C65" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C62" s="44"/>
-      <c r="D62" s="44"/>
-      <c r="E62" s="44"/>
-      <c r="F62" s="44"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="43" t="s">
+      <c r="D65" s="46"/>
+      <c r="E65" s="46"/>
+      <c r="F65" s="46"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="B63" s="44" t="s">
+      <c r="B66" s="45"/>
+      <c r="C66" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="C63" s="44"/>
-      <c r="D63" s="44"/>
-      <c r="E63" s="44"/>
-      <c r="F63" s="44"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="43" t="s">
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="B64" s="44" t="s">
+      <c r="B67" s="45"/>
+      <c r="C67" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="C64" s="44"/>
-      <c r="D64" s="44"/>
-      <c r="E64" s="44"/>
-      <c r="F64" s="44"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="46"/>
+      <c r="F67" s="46"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" s="45"/>
+      <c r="C68" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" s="46"/>
+      <c r="E68" s="46"/>
+      <c r="F68" s="46"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="B69" s="45"/>
+      <c r="C69" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69" s="46"/>
+      <c r="E69" s="46"/>
+      <c r="F69" s="46"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="B70" s="45"/>
+      <c r="C70" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70" s="46"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="46"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="B71" s="45"/>
+      <c r="C71" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" s="46"/>
+      <c r="E71" s="46"/>
+      <c r="F71" s="46"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" s="45"/>
+      <c r="C72" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
+      <c r="F72" s="46"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="B73" s="45"/>
+      <c r="C73" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="D73" s="46"/>
+      <c r="E73" s="46"/>
+      <c r="F73" s="46"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="B74" s="45"/>
+      <c r="C74" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74" s="46"/>
+      <c r="E74" s="46"/>
+      <c r="F74" s="46"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="B75" s="45"/>
+      <c r="C75" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="D75" s="46"/>
+      <c r="E75" s="46"/>
+      <c r="F75" s="46"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="B76" s="45"/>
+      <c r="C76" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" s="46"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="46"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="B77" s="45"/>
+      <c r="C77" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="D77" s="46"/>
+      <c r="E77" s="46"/>
+      <c r="F77" s="46"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="B78" s="45"/>
+      <c r="C78" s="46" t="s">
+        <v>110</v>
+      </c>
+      <c r="D78" s="46"/>
+      <c r="E78" s="46"/>
+      <c r="F78" s="46"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="B79" s="45"/>
+      <c r="C79" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" s="46"/>
+      <c r="E79" s="46"/>
+      <c r="F79" s="46"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="B80" s="45"/>
+      <c r="C80" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D80" s="46"/>
+      <c r="E80" s="46"/>
+      <c r="F80" s="46"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B81" s="45"/>
+      <c r="C81" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D81" s="46"/>
+      <c r="E81" s="46"/>
+      <c r="F81" s="46"/>
+    </row>
+    <row r="83" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+    </row>
+    <row r="84" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="B85" s="47"/>
+      <c r="C85" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="D85" s="48"/>
+      <c r="E85" s="48"/>
+      <c r="F85" s="49">
+        <v>93.4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="B86" s="50"/>
+      <c r="C86" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="D86" s="51"/>
+      <c r="E86" s="51"/>
+      <c r="F86" s="52">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="B87" s="47"/>
+      <c r="C87" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="49">
+        <v>44.540800000000004</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="B88" s="50"/>
+      <c r="C88" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="52">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" s="47"/>
+      <c r="C89" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="D89" s="48"/>
+      <c r="E89" s="48"/>
+      <c r="F89" s="53">
+        <v>8980</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="B90" s="50"/>
+      <c r="C90" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="D90" s="51"/>
+      <c r="E90" s="51"/>
+      <c r="F90" s="52">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="B91" s="47"/>
+      <c r="C91" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D91" s="48"/>
+      <c r="E91" s="48"/>
+      <c r="F91" s="54">
+        <v>541033.14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="B92" s="50"/>
+      <c r="C92" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="D92" s="51"/>
+      <c r="E92" s="51"/>
+      <c r="F92" s="55">
+        <v>10147.4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="B93" s="47"/>
+      <c r="C93" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="D93" s="48"/>
+      <c r="E93" s="48"/>
+      <c r="F93" s="54">
+        <v>18720</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B94" s="50"/>
+      <c r="C94" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="D94" s="51"/>
+      <c r="E94" s="51"/>
+      <c r="F94" s="55">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="B95" s="47"/>
+      <c r="C95" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D95" s="48"/>
+      <c r="E95" s="48"/>
+      <c r="F95" s="54">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="B96" s="50"/>
+      <c r="C96" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="D96" s="51"/>
+      <c r="E96" s="51"/>
+      <c r="F96" s="55">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="B97" s="47"/>
+      <c r="C97" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="D97" s="48"/>
+      <c r="E97" s="48"/>
+      <c r="F97" s="54">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="B98" s="50"/>
+      <c r="C98" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="D98" s="51"/>
+      <c r="E98" s="51"/>
+      <c r="F98" s="55">
+        <v>16216.320000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B99" s="47"/>
+      <c r="C99" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="D99" s="48"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="54">
+        <v>37360</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="B100" s="50"/>
+      <c r="C100" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="D100" s="51"/>
+      <c r="E100" s="51"/>
+      <c r="F100" s="55">
+        <v>6207.336000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="56" t="s">
+        <v>150</v>
+      </c>
+      <c r="B101" s="56"/>
+      <c r="C101" s="57" t="s">
+        <v>151</v>
+      </c>
+      <c r="D101" s="57"/>
+      <c r="E101" s="57"/>
+      <c r="F101" s="58">
+        <v>649484.196</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="B102" s="50"/>
+      <c r="C102" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="D102" s="51"/>
+      <c r="E102" s="51"/>
+      <c r="F102" s="55">
+        <v>4039.6661949275367</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="B103" s="47"/>
+      <c r="C103" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="D103" s="48"/>
+      <c r="E103" s="48"/>
+      <c r="F103" s="54">
+        <v>21061.172297826088</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="B104" s="50"/>
+      <c r="C104" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="D104" s="51"/>
+      <c r="E104" s="51"/>
+      <c r="F104" s="55">
+        <v>109816.16840579711</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="B105" s="47"/>
+      <c r="C105" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="D105" s="48"/>
+      <c r="E105" s="48"/>
+      <c r="F105" s="54">
+        <v>130877.3407036232</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="B106" s="50"/>
+      <c r="C106" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="D106" s="51"/>
+      <c r="E106" s="51"/>
+      <c r="F106" s="55">
+        <v>26916.53953850725</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="B107" s="56"/>
+      <c r="C107" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="D107" s="57"/>
+      <c r="E107" s="57"/>
+      <c r="F107" s="58">
+        <v>811317.742437058</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="B108" s="56"/>
+      <c r="C108" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="D108" s="57"/>
+      <c r="E108" s="57"/>
+      <c r="F108" s="58">
+        <v>680440.4017334348</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B110" s="11"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
+      <c r="F110" s="11"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="B111" s="45"/>
+      <c r="C111" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="D111" s="46"/>
+      <c r="E111" s="46"/>
+      <c r="F111" s="46"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="B112" s="45"/>
+      <c r="C112" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="D112" s="46"/>
+      <c r="E112" s="46"/>
+      <c r="F112" s="46"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="B113" s="45"/>
+      <c r="C113" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="D113" s="46"/>
+      <c r="E113" s="46"/>
+      <c r="F113" s="46"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="B114" s="45"/>
+      <c r="C114" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="D114" s="46"/>
+      <c r="E114" s="46"/>
+      <c r="F114" s="46"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="B115" s="45"/>
+      <c r="C115" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="D115" s="46"/>
+      <c r="E115" s="46"/>
+      <c r="F115" s="46"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B116" s="45"/>
+      <c r="C116" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="D116" s="46"/>
+      <c r="E116" s="46"/>
+      <c r="F116" s="46"/>
+    </row>
+    <row r="118" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="B118" s="43"/>
+      <c r="C118" s="43"/>
+      <c r="D118" s="43"/>
+      <c r="E118" s="43"/>
+      <c r="F118" s="43"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="B119" s="44"/>
+      <c r="C119" s="44"/>
+      <c r="D119" s="44"/>
+      <c r="E119" s="44"/>
+      <c r="F119" s="44"/>
+    </row>
+    <row r="121" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="59" t="s">
+        <v>54</v>
+      </c>
+      <c r="B121" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="C121" s="61" t="s">
+        <v>181</v>
+      </c>
+      <c r="D121" s="61"/>
+      <c r="E121" s="61"/>
+      <c r="F121" s="62">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="63" t="s">
+        <v>182</v>
+      </c>
+      <c r="B122" s="62">
+        <v>130</v>
+      </c>
+      <c r="C122" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="D122" s="61"/>
+      <c r="E122" s="61"/>
+      <c r="F122" s="62">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="123" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="63" t="s">
+        <v>184</v>
+      </c>
+      <c r="B123" s="62">
+        <v>45</v>
+      </c>
+      <c r="C123" s="61" t="s">
+        <v>185</v>
+      </c>
+      <c r="D123" s="61"/>
+      <c r="E123" s="61"/>
+      <c r="F123" s="62">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="124" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="59" t="s">
+        <v>186</v>
+      </c>
+      <c r="B124" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="C124" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="D124" s="61"/>
+      <c r="E124" s="61"/>
+      <c r="F124" s="62">
+        <v>207.28</v>
+      </c>
+    </row>
+    <row r="125" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="B125" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C125" s="61" t="s">
+        <v>190</v>
+      </c>
+      <c r="D125" s="61"/>
+      <c r="E125" s="61"/>
+      <c r="F125" s="62">
+        <v>40.14</v>
+      </c>
+    </row>
+    <row r="126" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="63" t="s">
+        <v>191</v>
+      </c>
+      <c r="B126" s="64" t="s">
+        <v>192</v>
+      </c>
+      <c r="C126" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="D126" s="61"/>
+      <c r="E126" s="61"/>
+      <c r="F126" s="62">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="127" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="63" t="s">
+        <v>194</v>
+      </c>
+      <c r="B127" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="C127" s="61" t="s">
+        <v>196</v>
+      </c>
+      <c r="D127" s="61"/>
+      <c r="E127" s="61"/>
+      <c r="F127" s="62">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="128" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="B128" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="C128" s="61" t="s">
+        <v>198</v>
+      </c>
+      <c r="D128" s="61"/>
+      <c r="E128" s="61"/>
+      <c r="F128" s="62">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="129" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="63" t="s">
+        <v>199</v>
+      </c>
+      <c r="B129" s="62">
+        <v>0</v>
+      </c>
+      <c r="C129" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D129" s="61"/>
+      <c r="E129" s="61"/>
+      <c r="F129" s="62">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="130" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="63" t="s">
+        <v>201</v>
+      </c>
+      <c r="B130" s="62">
+        <v>500</v>
+      </c>
+      <c r="C130" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="D130" s="61"/>
+      <c r="E130" s="61"/>
+      <c r="F130" s="62">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="131" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="B131" s="62">
+        <v>550</v>
+      </c>
+      <c r="C131" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="D131" s="61"/>
+      <c r="E131" s="61"/>
+      <c r="F131" s="62">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="132" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="B132" s="62">
+        <v>600</v>
+      </c>
+      <c r="C132" s="61" t="s">
+        <v>206</v>
+      </c>
+      <c r="D132" s="61"/>
+      <c r="E132" s="61"/>
+      <c r="F132" s="62">
+        <v>97.12</v>
+      </c>
+    </row>
+    <row r="133" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="63" t="s">
+        <v>207</v>
+      </c>
+      <c r="B133" s="62">
+        <v>650</v>
+      </c>
+      <c r="C133" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="D133" s="61"/>
+      <c r="E133" s="61"/>
+      <c r="F133" s="62">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="134" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="B134" s="62">
+        <v>700</v>
+      </c>
+      <c r="C134" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="D134" s="61"/>
+      <c r="E134" s="61"/>
+      <c r="F134" s="62">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="135" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="63" t="s">
+        <v>211</v>
+      </c>
+      <c r="B135" s="62">
+        <v>750</v>
+      </c>
+      <c r="C135" s="61" t="s">
+        <v>212</v>
+      </c>
+      <c r="D135" s="61"/>
+      <c r="E135" s="61"/>
+      <c r="F135" s="62">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="136" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="B136" s="62">
+        <v>800</v>
+      </c>
+      <c r="C136" s="61" t="s">
+        <v>214</v>
+      </c>
+      <c r="D136" s="61"/>
+      <c r="E136" s="61"/>
+      <c r="F136" s="62">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="137" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="B137" s="62">
+        <v>850</v>
+      </c>
+      <c r="C137" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="D137" s="61"/>
+      <c r="E137" s="61"/>
+      <c r="F137" s="62">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="138" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="59" t="s">
+        <v>217</v>
+      </c>
+      <c r="B138" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="C138" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="D138" s="61"/>
+      <c r="E138" s="61"/>
+      <c r="F138" s="62">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="139" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="B139" s="62">
+        <v>1170</v>
+      </c>
+      <c r="C139" s="61" t="s">
+        <v>220</v>
+      </c>
+      <c r="D139" s="61"/>
+      <c r="E139" s="61"/>
+      <c r="F139" s="62">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="140" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="63" t="s">
+        <v>221</v>
+      </c>
+      <c r="B140" s="62">
+        <v>1560</v>
+      </c>
+      <c r="C140" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="D140" s="61"/>
+      <c r="E140" s="61"/>
+      <c r="F140" s="62">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="141" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="B141" s="62">
+        <v>1820</v>
+      </c>
+      <c r="C141" s="61" t="s">
+        <v>224</v>
+      </c>
+      <c r="D141" s="61"/>
+      <c r="E141" s="61"/>
+      <c r="F141" s="62">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="142" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="63" t="s">
+        <v>225</v>
+      </c>
+      <c r="B142" s="62">
+        <v>3110</v>
+      </c>
+      <c r="C142" s="61" t="s">
+        <v>226</v>
+      </c>
+      <c r="D142" s="61"/>
+      <c r="E142" s="61"/>
+      <c r="F142" s="62">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="143" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="63" t="s">
+        <v>227</v>
+      </c>
+      <c r="B143" s="62">
+        <v>2340</v>
+      </c>
+      <c r="C143" s="61" t="s">
+        <v>228</v>
+      </c>
+      <c r="D143" s="61"/>
+      <c r="E143" s="61"/>
+      <c r="F143" s="62">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="144" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="63" t="s">
+        <v>229</v>
+      </c>
+      <c r="B144" s="62">
+        <v>10</v>
+      </c>
+      <c r="C144" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="D144" s="61"/>
+      <c r="E144" s="61"/>
+      <c r="F144" s="62">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="145" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="B145" s="62">
+        <v>20</v>
+      </c>
+      <c r="C145" s="61" t="s">
+        <v>232</v>
+      </c>
+      <c r="D145" s="61"/>
+      <c r="E145" s="61"/>
+      <c r="F145" s="62">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="146" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="B146" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="C146" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="D146" s="61"/>
+      <c r="E146" s="61"/>
+      <c r="F146" s="62">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="147" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="B147" s="62">
+        <v>45</v>
+      </c>
+      <c r="C147" t="s">
+        <v>48</v>
+      </c>
+      <c r="D147"/>
+      <c r="E147"/>
+      <c r="F147" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="198">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -2509,1123 +3448,150 @@
     <mergeCell ref="A55:C55"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:F64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="C67:F67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:F68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:F80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:F81"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:E103"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="C111:F111"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="C112:F112"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:F113"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="C114:F114"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="C115:F115"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="C116:F116"/>
+    <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C124:E124"/>
+    <mergeCell ref="C125:E125"/>
+    <mergeCell ref="C126:E126"/>
+    <mergeCell ref="C127:E127"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="C130:E130"/>
+    <mergeCell ref="C131:E131"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="C143:E143"/>
+    <mergeCell ref="C144:E144"/>
+    <mergeCell ref="C145:E145"/>
+    <mergeCell ref="C146:E146"/>
+    <mergeCell ref="C147:E147"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="78" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;8ul. Brzozowa 9, Poznań&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
   </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="5" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="B15" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="B18" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="B20" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="B21" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="B24" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-    </row>
-    <row r="27" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="47" t="s">
-        <v>133</v>
-      </c>
-      <c r="B28" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="49">
-        <v>93.4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="B29" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="B30" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="49">
-        <v>44.540800000000004</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="B31" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="52">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="47" t="s">
-        <v>141</v>
-      </c>
-      <c r="B32" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="53">
-        <v>8980</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="B33" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="52">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="47" t="s">
-        <v>145</v>
-      </c>
-      <c r="B34" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="54">
-        <v>541033.14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="B35" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="55">
-        <v>10147.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="47" t="s">
-        <v>149</v>
-      </c>
-      <c r="B36" s="48" t="s">
-        <v>150</v>
-      </c>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="54">
-        <v>18720</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="50" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="55">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="B38" s="48" t="s">
-        <v>153</v>
-      </c>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="54">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="B39" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="55">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="B40" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="54">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="B41" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="55">
-        <v>16216.320000000002</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="B42" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="54">
-        <v>37360</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="B43" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="55">
-        <v>6207.336000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="B44" s="57" t="s">
-        <v>164</v>
-      </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="58">
-        <v>649484.196</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="B45" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="55">
-        <v>4039.6661949275367</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="B46" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="54">
-        <v>21061.172297826088</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="50" t="s">
-        <v>169</v>
-      </c>
-      <c r="B47" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="55">
-        <v>109816.16840579711</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="47" t="s">
-        <v>171</v>
-      </c>
-      <c r="B48" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="54">
-        <v>130877.3407036232</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="50" t="s">
-        <v>173</v>
-      </c>
-      <c r="B49" s="51" t="s">
-        <v>174</v>
-      </c>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="55">
-        <v>26916.53953850725</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="56" t="s">
-        <v>175</v>
-      </c>
-      <c r="B50" s="57" t="s">
-        <v>176</v>
-      </c>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="58">
-        <v>811317.742437058</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="56" t="s">
-        <v>177</v>
-      </c>
-      <c r="B51" s="57" t="s">
-        <v>178</v>
-      </c>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="58">
-        <v>680440.4017334348</v>
-      </c>
-    </row>
-    <row r="52" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="45"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="B53" s="46"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="46"/>
-    </row>
-    <row r="55" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="59" t="s">
-        <v>54</v>
-      </c>
-      <c r="B55" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C55" s="61" t="s">
-        <v>181</v>
-      </c>
-      <c r="D55" s="61"/>
-      <c r="E55" s="62">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="61" t="s">
-        <v>182</v>
-      </c>
-      <c r="B56" s="62">
-        <v>130</v>
-      </c>
-      <c r="C56" s="61" t="s">
-        <v>183</v>
-      </c>
-      <c r="D56" s="61"/>
-      <c r="E56" s="62">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="57" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="61" t="s">
-        <v>184</v>
-      </c>
-      <c r="B57" s="62">
-        <v>45</v>
-      </c>
-      <c r="C57" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="D57" s="61"/>
-      <c r="E57" s="62">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="58" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="59" t="s">
-        <v>186</v>
-      </c>
-      <c r="B58" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C58" s="61" t="s">
-        <v>187</v>
-      </c>
-      <c r="D58" s="61"/>
-      <c r="E58" s="62">
-        <v>207.28</v>
-      </c>
-    </row>
-    <row r="59" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="61" t="s">
-        <v>188</v>
-      </c>
-      <c r="B59" s="63" t="s">
-        <v>189</v>
-      </c>
-      <c r="C59" s="61" t="s">
-        <v>190</v>
-      </c>
-      <c r="D59" s="61"/>
-      <c r="E59" s="62">
-        <v>40.14</v>
-      </c>
-    </row>
-    <row r="60" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="B60" s="63" t="s">
-        <v>192</v>
-      </c>
-      <c r="C60" s="61" t="s">
-        <v>193</v>
-      </c>
-      <c r="D60" s="61"/>
-      <c r="E60" s="62">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="61" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="61" t="s">
-        <v>194</v>
-      </c>
-      <c r="B61" s="63" t="s">
-        <v>195</v>
-      </c>
-      <c r="C61" s="61" t="s">
-        <v>196</v>
-      </c>
-      <c r="D61" s="61"/>
-      <c r="E61" s="62">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="62" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="B62" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C62" s="61" t="s">
-        <v>198</v>
-      </c>
-      <c r="D62" s="61"/>
-      <c r="E62" s="62">
-        <v>10.95</v>
-      </c>
-    </row>
-    <row r="63" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="61" t="s">
-        <v>199</v>
-      </c>
-      <c r="B63" s="62">
-        <v>0</v>
-      </c>
-      <c r="C63" s="61" t="s">
-        <v>200</v>
-      </c>
-      <c r="D63" s="61"/>
-      <c r="E63" s="62">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="64" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="B64" s="62">
-        <v>500</v>
-      </c>
-      <c r="C64" s="61" t="s">
-        <v>202</v>
-      </c>
-      <c r="D64" s="61"/>
-      <c r="E64" s="62">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="65" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="61" t="s">
-        <v>203</v>
-      </c>
-      <c r="B65" s="62">
-        <v>550</v>
-      </c>
-      <c r="C65" s="61" t="s">
-        <v>204</v>
-      </c>
-      <c r="D65" s="61"/>
-      <c r="E65" s="62">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="66" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="61" t="s">
-        <v>205</v>
-      </c>
-      <c r="B66" s="62">
-        <v>600</v>
-      </c>
-      <c r="C66" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="D66" s="61"/>
-      <c r="E66" s="62">
-        <v>97.12</v>
-      </c>
-    </row>
-    <row r="67" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="61" t="s">
-        <v>207</v>
-      </c>
-      <c r="B67" s="62">
-        <v>650</v>
-      </c>
-      <c r="C67" s="61" t="s">
-        <v>208</v>
-      </c>
-      <c r="D67" s="61"/>
-      <c r="E67" s="62">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="68" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="61" t="s">
-        <v>209</v>
-      </c>
-      <c r="B68" s="62">
-        <v>700</v>
-      </c>
-      <c r="C68" s="61" t="s">
-        <v>210</v>
-      </c>
-      <c r="D68" s="61"/>
-      <c r="E68" s="62">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="69" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="B69" s="62">
-        <v>750</v>
-      </c>
-      <c r="C69" s="61" t="s">
-        <v>212</v>
-      </c>
-      <c r="D69" s="61"/>
-      <c r="E69" s="62">
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="70" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="61" t="s">
-        <v>213</v>
-      </c>
-      <c r="B70" s="62">
-        <v>800</v>
-      </c>
-      <c r="C70" s="61" t="s">
-        <v>214</v>
-      </c>
-      <c r="D70" s="61"/>
-      <c r="E70" s="62">
-        <v>8.08</v>
-      </c>
-    </row>
-    <row r="71" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="61" t="s">
-        <v>215</v>
-      </c>
-      <c r="B71" s="62">
-        <v>850</v>
-      </c>
-      <c r="C71" s="61" t="s">
-        <v>216</v>
-      </c>
-      <c r="D71" s="61"/>
-      <c r="E71" s="62">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="72" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="59" t="s">
-        <v>217</v>
-      </c>
-      <c r="B72" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C72" s="61" t="s">
-        <v>218</v>
-      </c>
-      <c r="D72" s="61"/>
-      <c r="E72" s="62">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="73" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="61" t="s">
-        <v>219</v>
-      </c>
-      <c r="B73" s="62">
-        <v>1170</v>
-      </c>
-      <c r="C73" s="61" t="s">
-        <v>220</v>
-      </c>
-      <c r="D73" s="61"/>
-      <c r="E73" s="62">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="74" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="61" t="s">
-        <v>221</v>
-      </c>
-      <c r="B74" s="62">
-        <v>1560</v>
-      </c>
-      <c r="C74" s="61" t="s">
-        <v>222</v>
-      </c>
-      <c r="D74" s="61"/>
-      <c r="E74" s="62">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="75" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="61" t="s">
-        <v>223</v>
-      </c>
-      <c r="B75" s="62">
-        <v>1820</v>
-      </c>
-      <c r="C75" s="61" t="s">
-        <v>224</v>
-      </c>
-      <c r="D75" s="61"/>
-      <c r="E75" s="62">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="76" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="B76" s="62">
-        <v>3110</v>
-      </c>
-      <c r="C76" s="61" t="s">
-        <v>226</v>
-      </c>
-      <c r="D76" s="61"/>
-      <c r="E76" s="62">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="77" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="61" t="s">
-        <v>227</v>
-      </c>
-      <c r="B77" s="62">
-        <v>2340</v>
-      </c>
-      <c r="C77" s="61" t="s">
-        <v>228</v>
-      </c>
-      <c r="D77" s="61"/>
-      <c r="E77" s="62">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="78" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="61" t="s">
-        <v>229</v>
-      </c>
-      <c r="B78" s="62">
-        <v>10</v>
-      </c>
-      <c r="C78" s="61" t="s">
-        <v>230</v>
-      </c>
-      <c r="D78" s="61"/>
-      <c r="E78" s="62">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="79" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="61" t="s">
-        <v>231</v>
-      </c>
-      <c r="B79" s="62">
-        <v>20</v>
-      </c>
-      <c r="C79" s="61" t="s">
-        <v>232</v>
-      </c>
-      <c r="D79" s="61"/>
-      <c r="E79" s="62">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="80" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="59" t="s">
-        <v>233</v>
-      </c>
-      <c r="B80" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C80" s="61" t="s">
-        <v>234</v>
-      </c>
-      <c r="D80" s="61"/>
-      <c r="E80" s="62">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="81" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="61" t="s">
-        <v>235</v>
-      </c>
-      <c r="B81" s="62">
-        <v>45</v>
-      </c>
-      <c r="C81" t="s">
-        <v>48</v>
-      </c>
-      <c r="D81"/>
-      <c r="E81" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-  </mergeCells>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="82" fitToWidth="1" fitToHeight="1"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8ul. Brzozowa 9, Poznań&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="51" max="16838" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="57" max="16838" man="1"/>
+    <brk id="117" max="16838" man="1"/>
   </rowBreaks>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Brzozowa_9_Poznan_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Brzozowa_9_Poznan_NK38.xlsx
@@ -22,10 +22,10 @@
     <t>ul. Brzozowa 9, Poznań</t>
   </si>
   <si>
-    <t>21.10.2026, 10:28</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 10:28:00 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 11:44</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 11:44:46 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena</t>
@@ -945,7 +945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -1130,8 +1130,11 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="3"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" indent="3"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2971,7 +2974,7 @@
       <c r="A122" s="63" t="s">
         <v>182</v>
       </c>
-      <c r="B122" s="62">
+      <c r="B122" s="64">
         <v>130</v>
       </c>
       <c r="C122" s="61" t="s">
@@ -2987,7 +2990,7 @@
       <c r="A123" s="63" t="s">
         <v>184</v>
       </c>
-      <c r="B123" s="62">
+      <c r="B123" s="64">
         <v>45</v>
       </c>
       <c r="C123" s="61" t="s">
@@ -3019,7 +3022,7 @@
       <c r="A125" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="B125" s="64" t="s">
+      <c r="B125" s="65" t="s">
         <v>189</v>
       </c>
       <c r="C125" s="61" t="s">
@@ -3035,7 +3038,7 @@
       <c r="A126" s="63" t="s">
         <v>191</v>
       </c>
-      <c r="B126" s="64" t="s">
+      <c r="B126" s="65" t="s">
         <v>192</v>
       </c>
       <c r="C126" s="61" t="s">
@@ -3051,7 +3054,7 @@
       <c r="A127" s="63" t="s">
         <v>194</v>
       </c>
-      <c r="B127" s="64" t="s">
+      <c r="B127" s="65" t="s">
         <v>195</v>
       </c>
       <c r="C127" s="61" t="s">
@@ -3083,7 +3086,7 @@
       <c r="A129" s="63" t="s">
         <v>199</v>
       </c>
-      <c r="B129" s="62">
+      <c r="B129" s="64">
         <v>0</v>
       </c>
       <c r="C129" s="61" t="s">
@@ -3099,7 +3102,7 @@
       <c r="A130" s="63" t="s">
         <v>201</v>
       </c>
-      <c r="B130" s="62">
+      <c r="B130" s="64">
         <v>500</v>
       </c>
       <c r="C130" s="61" t="s">
@@ -3115,7 +3118,7 @@
       <c r="A131" s="63" t="s">
         <v>203</v>
       </c>
-      <c r="B131" s="62">
+      <c r="B131" s="64">
         <v>550</v>
       </c>
       <c r="C131" s="61" t="s">
@@ -3131,7 +3134,7 @@
       <c r="A132" s="63" t="s">
         <v>205</v>
       </c>
-      <c r="B132" s="62">
+      <c r="B132" s="64">
         <v>600</v>
       </c>
       <c r="C132" s="61" t="s">
@@ -3147,7 +3150,7 @@
       <c r="A133" s="63" t="s">
         <v>207</v>
       </c>
-      <c r="B133" s="62">
+      <c r="B133" s="64">
         <v>650</v>
       </c>
       <c r="C133" s="61" t="s">
@@ -3163,7 +3166,7 @@
       <c r="A134" s="63" t="s">
         <v>209</v>
       </c>
-      <c r="B134" s="62">
+      <c r="B134" s="64">
         <v>700</v>
       </c>
       <c r="C134" s="61" t="s">
@@ -3179,7 +3182,7 @@
       <c r="A135" s="63" t="s">
         <v>211</v>
       </c>
-      <c r="B135" s="62">
+      <c r="B135" s="64">
         <v>750</v>
       </c>
       <c r="C135" s="61" t="s">
@@ -3195,7 +3198,7 @@
       <c r="A136" s="63" t="s">
         <v>213</v>
       </c>
-      <c r="B136" s="62">
+      <c r="B136" s="64">
         <v>800</v>
       </c>
       <c r="C136" s="61" t="s">
@@ -3211,7 +3214,7 @@
       <c r="A137" s="63" t="s">
         <v>215</v>
       </c>
-      <c r="B137" s="62">
+      <c r="B137" s="64">
         <v>850</v>
       </c>
       <c r="C137" s="61" t="s">
@@ -3243,7 +3246,7 @@
       <c r="A139" s="63" t="s">
         <v>219</v>
       </c>
-      <c r="B139" s="62">
+      <c r="B139" s="64">
         <v>1170</v>
       </c>
       <c r="C139" s="61" t="s">
@@ -3259,7 +3262,7 @@
       <c r="A140" s="63" t="s">
         <v>221</v>
       </c>
-      <c r="B140" s="62">
+      <c r="B140" s="64">
         <v>1560</v>
       </c>
       <c r="C140" s="61" t="s">
@@ -3275,7 +3278,7 @@
       <c r="A141" s="63" t="s">
         <v>223</v>
       </c>
-      <c r="B141" s="62">
+      <c r="B141" s="64">
         <v>1820</v>
       </c>
       <c r="C141" s="61" t="s">
@@ -3291,7 +3294,7 @@
       <c r="A142" s="63" t="s">
         <v>225</v>
       </c>
-      <c r="B142" s="62">
+      <c r="B142" s="64">
         <v>3110</v>
       </c>
       <c r="C142" s="61" t="s">
@@ -3307,7 +3310,7 @@
       <c r="A143" s="63" t="s">
         <v>227</v>
       </c>
-      <c r="B143" s="62">
+      <c r="B143" s="64">
         <v>2340</v>
       </c>
       <c r="C143" s="61" t="s">
@@ -3323,7 +3326,7 @@
       <c r="A144" s="63" t="s">
         <v>229</v>
       </c>
-      <c r="B144" s="62">
+      <c r="B144" s="64">
         <v>10</v>
       </c>
       <c r="C144" s="61" t="s">
@@ -3339,7 +3342,7 @@
       <c r="A145" s="63" t="s">
         <v>231</v>
       </c>
-      <c r="B145" s="62">
+      <c r="B145" s="64">
         <v>20</v>
       </c>
       <c r="C145" s="61" t="s">
@@ -3371,7 +3374,7 @@
       <c r="A147" s="63" t="s">
         <v>235</v>
       </c>
-      <c r="B147" s="62">
+      <c r="B147" s="64">
         <v>45</v>
       </c>
       <c r="C147" t="s">

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Brzozowa_9_Poznan_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Brzozowa_9_Poznan_NK38.xlsx
@@ -22,10 +22,10 @@
     <t>ul. Brzozowa 9, Poznań</t>
   </si>
   <si>
-    <t>21.10.2026, 11:44</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 11:44:46 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 12:42</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 12:42:34 · ceny netto w zł · szablon NK38</t>
   </si>
   <si>
     <t>Cena</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Brzozowa_9_Poznan_NK38.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Brzozowa_9_Poznan_NK38.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="237">
   <si>
     <t>KALKULACJA NK38</t>
   </si>
@@ -22,10 +22,10 @@
     <t>ul. Brzozowa 9, Poznań</t>
   </si>
   <si>
-    <t>21.10.2026, 12:42</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 12:42:34 · ceny netto w zł · szablon NK38</t>
+    <t>21.10.2026, 12:45</t>
+  </si>
+  <si>
+    <t>Ceny netto · wygenerowano 30.10.2026</t>
   </si>
   <si>
     <t>Cena</t>
@@ -40,7 +40,10 @@
     <t>Rabat od oferty</t>
   </si>
   <si>
-    <t>Cena ofertowa · zysk 14% · 2000 kg · 3350 € / MP</t>
+    <t>Cena ofertowa · zysk 14% · 2000 kg</t>
+  </si>
+  <si>
+    <t>14 488 zł · 3350 €</t>
   </si>
   <si>
     <t>–</t>
@@ -52,7 +55,7 @@
     <t>−41 182 zł (−5,08%)</t>
   </si>
   <si>
-    <t>Próg opłacalności · zysk 0% (maks. rabat)</t>
+    <t>Próg opłacalności · zysk 0% · maks. rabat</t>
   </si>
   <si>
     <t>−129 247 zł (−15,93%)</t>
@@ -64,7 +67,7 @@
     <t xml:space="preserve">   w tym Pozycja 2 · 12× NK41</t>
   </si>
   <si>
-    <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
+    <t>Pole do negocjacji (2000 kg)</t>
   </si>
   <si>
     <t>Zysk</t>
@@ -94,76 +97,76 @@
     <t>NK38 · Zagłębienie</t>
   </si>
   <si>
+    <t>Prześwit</t>
+  </si>
+  <si>
     <t>4× NK38-S + 6× NK38-D = 32 MP</t>
   </si>
   <si>
     <t>H1 190 / H2 195 cm, dł. 530</t>
   </si>
   <si>
+    <t>P 360 cm</t>
+  </si>
+  <si>
     <t>Agregaty</t>
   </si>
   <si>
-    <t>Prześwit</t>
+    <t>NK38 · Wysokość pojazdów</t>
   </si>
   <si>
     <t>2 szt.</t>
   </si>
   <si>
-    <t>P 360 cm</t>
+    <t>▲ 165 cm    ▼ 175 cm</t>
   </si>
   <si>
     <t>Pozycja 2 · NK41</t>
   </si>
   <si>
-    <t>NK38 · Wysokość pojazdów</t>
+    <t>NK41 · Prześwit</t>
   </si>
   <si>
     <t>12× NK41 = 24 MP</t>
   </si>
   <si>
-    <t>▲ 165 cm    ▼ 175 cm</t>
-  </si>
-  <si>
-    <t>NK41 · Prześwit</t>
+    <t>P 280 cm</t>
+  </si>
+  <si>
+    <t>NK41 · Wysokość pojazdów</t>
+  </si>
+  <si>
+    <t>Długość miejsca</t>
   </si>
   <si>
     <t>3 szt. (2× 3 kW, 1× 6 kW)</t>
   </si>
   <si>
-    <t>P 280 cm</t>
+    <t>▲ 150 cm    ▼ 150 cm</t>
+  </si>
+  <si>
+    <t>400 cm</t>
   </si>
   <si>
     <t>Razem</t>
   </si>
   <si>
-    <t>NK41 · Wysokość pojazdów</t>
+    <t>KOB / GDW</t>
   </si>
   <si>
     <t>22 urządzenia = 56 miejsc postojowych</t>
   </si>
   <si>
-    <t>▲ 150 cm    ▼ 150 cm</t>
+    <t>0,515% / 2,685%</t>
   </si>
   <si>
     <t>Barierki / maskownice / magistrala</t>
   </si>
   <si>
-    <t>Długość miejsca</t>
+    <t/>
   </si>
   <si>
     <t>barierki 6 · maskownice 0 · magistrala 0 × 6 m</t>
-  </si>
-  <si>
-    <t>400 cm</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>KOB / GDW</t>
-  </si>
-  <si>
-    <t>0,515% / 2,685%</t>
   </si>
   <si>
     <t>Opis wariantu</t>
@@ -735,7 +738,7 @@
     <numFmt numFmtId="170" formatCode="&quot;+&quot;#,##0 &quot;zł&quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -745,98 +748,104 @@
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="8"/>
-      <name val="Arial"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="16"/>
-      <name val="Arial"/>
+      <sz val="17.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="13"/>
-      <name val="Arial"/>
+      <sz val="14.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="9"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF0E171C"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0E171C"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF13794A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FFB42318"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF6A7780"/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0A6B74"/>
       <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0E171C"/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF13794A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFB42318"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF6A7780"/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="8"/>
-      <name val="Arial"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="11"/>
-      <name val="Arial"/>
+      <sz val="11.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF6A7780"/>
-      <sz val="9"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF0E171C"/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -882,7 +891,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -915,12 +924,58 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
       <top style="thin">
         <color rgb="FFD3D9DD"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD3D9DD"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -945,7 +1000,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -1033,21 +1088,36 @@
       <alignment wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1077,7 +1147,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1113,27 +1183,27 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="3"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="3"/>
     </xf>
   </cellXfs>
@@ -1475,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1545,16 +1615,16 @@
       <c r="D6" s="9">
         <v>811317.742437058</v>
       </c>
-      <c r="E6" s="9">
-        <v>14487.81682923318</v>
+      <c r="E6" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1565,12 +1635,12 @@
         <v>13752.421982263908</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1581,12 +1651,12 @@
         <v>12179.83176198871</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -1597,12 +1667,12 @@
         <v>17077.336015029137</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -1613,12 +1683,12 @@
         <v>11035.124581505237</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1628,7 +1698,7 @@
     </row>
     <row r="13" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>6</v>
@@ -1637,10 +1707,10 @@
         <v>8</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>7</v>
@@ -1808,7 +1878,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="29"/>
@@ -1818,7 +1888,7 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -1828,1566 +1898,1558 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="30"/>
       <c r="C25" s="30"/>
       <c r="D25" s="30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="30"/>
     </row>
     <row r="26" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
-      <c r="D26" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
+      <c r="D26" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
+      <c r="A27" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="35"/>
+      <c r="F27" s="36" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="28" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="31" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B28" s="31"/>
       <c r="C28" s="31"/>
       <c r="D28" s="31" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E28" s="31"/>
       <c r="F28" s="31"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
+      <c r="A29" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
     </row>
     <row r="30" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="31" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E30" s="31"/>
       <c r="F30" s="31"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
+      <c r="A31" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
     </row>
     <row r="32" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="31" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
-      <c r="D32" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
+      <c r="D32" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="32"/>
+      <c r="F32" s="33" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
+      <c r="A33" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="F33" s="36" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="34" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="31" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E34" s="31"/>
       <c r="F34" s="31"/>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="33"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
+      <c r="A35" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
     </row>
     <row r="36" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="31" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E36" s="31"/>
       <c r="F36" s="31"/>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-    </row>
-    <row r="38" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-    </row>
-    <row r="39" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33" t="s">
+      <c r="A37" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-    </row>
-    <row r="41" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="B41" s="35" t="s">
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="36" t="s">
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+    </row>
+    <row r="40" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="36"/>
-      <c r="C42" s="36" t="s">
+      <c r="B40" s="40"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36" t="s">
+      <c r="B41" s="41"/>
+      <c r="C41" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="36"/>
-    </row>
-    <row r="43" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="37" t="s">
+      <c r="D41" s="41"/>
+      <c r="E41" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37" t="s">
+      <c r="F41" s="41"/>
+    </row>
+    <row r="42" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37" t="s">
+      <c r="B42" s="42"/>
+      <c r="C42" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F43" s="37"/>
-    </row>
-    <row r="45" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
+      <c r="D42" s="42"/>
+      <c r="E42" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="F42" s="42"/>
+    </row>
+    <row r="44" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="13" t="s">
+      <c r="B44" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="13" t="s">
         <v>62</v>
       </c>
+      <c r="F44" s="13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="45" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="B46" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="39"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="40" t="s">
-        <v>10</v>
+      <c r="A46" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="45">
+        <v>144784.1435695556</v>
+      </c>
+      <c r="F46" s="45">
+        <v>137456.15870459902</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="39"/>
-      <c r="D47" s="39"/>
-      <c r="E47" s="40">
-        <v>144784.1435695556</v>
-      </c>
-      <c r="F47" s="40">
-        <v>137456.15870459902</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B48" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="40">
+      <c r="A47" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="B47" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="45">
         <v>133234.42053140095</v>
       </c>
-      <c r="F48" s="40">
+      <c r="F47" s="45">
         <v>126399.10161290324</v>
       </c>
     </row>
-    <row r="50" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="13" t="s">
+    <row r="49" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E50" s="13" t="s">
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="F50" s="13" t="s">
+      <c r="E49" s="13" t="s">
         <v>71</v>
       </c>
+      <c r="F49" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="46">
+        <v>1540</v>
+      </c>
+      <c r="E50" s="46">
+        <v>18480</v>
+      </c>
+      <c r="F50" s="46">
+        <v>9240</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="41">
-        <v>1540</v>
-      </c>
-      <c r="E51" s="41">
-        <v>18480</v>
-      </c>
-      <c r="F51" s="41">
-        <v>9240</v>
+      <c r="A51" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B51" s="47"/>
+      <c r="C51" s="47"/>
+      <c r="D51" s="9">
+        <v>1760</v>
+      </c>
+      <c r="E51" s="9">
+        <v>21120</v>
+      </c>
+      <c r="F51" s="9">
+        <v>10560</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="B52" s="42"/>
-      <c r="C52" s="42"/>
-      <c r="D52" s="9">
-        <v>1760</v>
-      </c>
-      <c r="E52" s="9">
-        <v>21120</v>
-      </c>
-      <c r="F52" s="9">
-        <v>10560</v>
+      <c r="A52" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="46">
+        <v>1980</v>
+      </c>
+      <c r="E52" s="46">
+        <v>23760</v>
+      </c>
+      <c r="F52" s="46">
+        <v>11880</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="41">
-        <v>1980</v>
-      </c>
-      <c r="E53" s="41">
-        <v>23760</v>
-      </c>
-      <c r="F53" s="41">
-        <v>11880</v>
+      <c r="A53" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B53" s="47"/>
+      <c r="C53" s="47"/>
+      <c r="D53" s="9">
+        <v>2200</v>
+      </c>
+      <c r="E53" s="9">
+        <v>26400</v>
+      </c>
+      <c r="F53" s="9">
+        <v>13200</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="B54" s="42"/>
-      <c r="C54" s="42"/>
-      <c r="D54" s="9">
-        <v>2200</v>
-      </c>
-      <c r="E54" s="9">
-        <v>26400</v>
-      </c>
-      <c r="F54" s="9">
-        <v>13200</v>
+      <c r="A54" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="46">
+        <v>2420</v>
+      </c>
+      <c r="E54" s="46">
+        <v>29040</v>
+      </c>
+      <c r="F54" s="46">
+        <v>14520</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
-      <c r="D55" s="41">
-        <v>2420</v>
-      </c>
-      <c r="E55" s="41">
-        <v>29040</v>
-      </c>
-      <c r="F55" s="41">
-        <v>14520</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="41">
+      <c r="D55" s="46">
         <v>2640</v>
       </c>
-      <c r="E56" s="41">
+      <c r="E55" s="46">
         <v>31680</v>
       </c>
-      <c r="F56" s="41">
+      <c r="F55" s="46">
         <v>15840</v>
       </c>
     </row>
-    <row r="58" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="B58" s="43"/>
-      <c r="C58" s="43"/>
-      <c r="D58" s="43"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="43"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="44" t="s">
+    <row r="57" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="B59" s="44"/>
-      <c r="C59" s="44"/>
-      <c r="D59" s="44"/>
-      <c r="E59" s="44"/>
-      <c r="F59" s="44"/>
-    </row>
-    <row r="61" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
+      <c r="B57" s="48"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="48"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+    </row>
+    <row r="60" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" s="50"/>
+      <c r="C61" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D61" s="51"/>
+      <c r="E61" s="51"/>
+      <c r="F61" s="51"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="B62" s="45"/>
-      <c r="C62" s="46" t="s">
-        <v>48</v>
-      </c>
-      <c r="D62" s="46"/>
-      <c r="E62" s="46"/>
-      <c r="F62" s="46"/>
+      <c r="A62" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="50"/>
+      <c r="C62" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62" s="51"/>
+      <c r="E62" s="51"/>
+      <c r="F62" s="51"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="B63" s="45"/>
-      <c r="C63" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="D63" s="46"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="46"/>
+      <c r="A63" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" s="50"/>
+      <c r="C63" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" s="51"/>
+      <c r="E63" s="51"/>
+      <c r="F63" s="51"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="B64" s="45"/>
-      <c r="C64" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="D64" s="46"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="46"/>
+      <c r="A64" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B64" s="50"/>
+      <c r="C64" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="D64" s="51"/>
+      <c r="E64" s="51"/>
+      <c r="F64" s="51"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="B65" s="45"/>
-      <c r="C65" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="D65" s="46"/>
-      <c r="E65" s="46"/>
-      <c r="F65" s="46"/>
+      <c r="A65" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="B65" s="50"/>
+      <c r="C65" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="D65" s="51"/>
+      <c r="E65" s="51"/>
+      <c r="F65" s="51"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="B66" s="45"/>
-      <c r="C66" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
+      <c r="A66" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="B66" s="50"/>
+      <c r="C66" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="D66" s="51"/>
+      <c r="E66" s="51"/>
+      <c r="F66" s="51"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="B67" s="45"/>
-      <c r="C67" s="46" t="s">
+      <c r="A67" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="50"/>
+      <c r="C67" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="D67" s="51"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="51"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B68" s="50"/>
+      <c r="C68" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="D68" s="51"/>
+      <c r="E68" s="51"/>
+      <c r="F68" s="51"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B69" s="50"/>
+      <c r="C69" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D69" s="51"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="51"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B70" s="50"/>
+      <c r="C70" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71" s="50"/>
+      <c r="C71" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B72" s="50"/>
+      <c r="C72" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="D72" s="51"/>
+      <c r="E72" s="51"/>
+      <c r="F72" s="51"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B73" s="50"/>
+      <c r="C73" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D73" s="51"/>
+      <c r="E73" s="51"/>
+      <c r="F73" s="51"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="B74" s="50"/>
+      <c r="C74" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="D74" s="51"/>
+      <c r="E74" s="51"/>
+      <c r="F74" s="51"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="B75" s="50"/>
+      <c r="C75" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="D75" s="51"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="51"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B76" s="50"/>
+      <c r="C76" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D76" s="51"/>
+      <c r="E76" s="51"/>
+      <c r="F76" s="51"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" s="50"/>
+      <c r="C77" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="D77" s="51"/>
+      <c r="E77" s="51"/>
+      <c r="F77" s="51"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" s="50"/>
+      <c r="C78" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="D78" s="51"/>
+      <c r="E78" s="51"/>
+      <c r="F78" s="51"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B79" s="50"/>
+      <c r="C79" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="D79" s="51"/>
+      <c r="E79" s="51"/>
+      <c r="F79" s="51"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="B80" s="50"/>
+      <c r="C80" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="D80" s="51"/>
+      <c r="E80" s="51"/>
+      <c r="F80" s="51"/>
+    </row>
+    <row r="82" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+    </row>
+    <row r="83" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="B84" s="52"/>
+      <c r="C84" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="D84" s="53"/>
+      <c r="E84" s="53"/>
+      <c r="F84" s="54">
+        <v>93.4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="B85" s="55"/>
+      <c r="C85" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="D85" s="56"/>
+      <c r="E85" s="56"/>
+      <c r="F85" s="57">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="B86" s="52"/>
+      <c r="C86" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D86" s="53"/>
+      <c r="E86" s="53"/>
+      <c r="F86" s="54">
+        <v>44.540800000000004</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="55" t="s">
+        <v>127</v>
+      </c>
+      <c r="B87" s="55"/>
+      <c r="C87" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="D87" s="56"/>
+      <c r="E87" s="56"/>
+      <c r="F87" s="57">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="B88" s="52"/>
+      <c r="C88" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="58">
+        <v>8980</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="B89" s="55"/>
+      <c r="C89" s="56" t="s">
+        <v>132</v>
+      </c>
+      <c r="D89" s="56"/>
+      <c r="E89" s="56"/>
+      <c r="F89" s="57">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="B90" s="52"/>
+      <c r="C90" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D90" s="53"/>
+      <c r="E90" s="53"/>
+      <c r="F90" s="59">
+        <v>541033.14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="B91" s="55"/>
+      <c r="C91" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="D91" s="56"/>
+      <c r="E91" s="56"/>
+      <c r="F91" s="60">
+        <v>10147.4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="B92" s="52"/>
+      <c r="C92" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="D92" s="53"/>
+      <c r="E92" s="53"/>
+      <c r="F92" s="59">
+        <v>18720</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B93" s="55"/>
+      <c r="C93" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="D93" s="56"/>
+      <c r="E93" s="56"/>
+      <c r="F93" s="60">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="B94" s="52"/>
+      <c r="C94" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="D94" s="53"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="59">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="B95" s="55"/>
+      <c r="C95" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="D95" s="56"/>
+      <c r="E95" s="56"/>
+      <c r="F95" s="60">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="B96" s="52"/>
+      <c r="C96" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="D96" s="53"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="59">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="B97" s="55"/>
+      <c r="C97" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="D97" s="56"/>
+      <c r="E97" s="56"/>
+      <c r="F97" s="60">
+        <v>16216.320000000002</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="B98" s="52"/>
+      <c r="C98" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="D98" s="53"/>
+      <c r="E98" s="53"/>
+      <c r="F98" s="59">
+        <v>37360</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="B99" s="55"/>
+      <c r="C99" s="56" t="s">
+        <v>150</v>
+      </c>
+      <c r="D99" s="56"/>
+      <c r="E99" s="56"/>
+      <c r="F99" s="60">
+        <v>6207.336000000001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="B100" s="61"/>
+      <c r="C100" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="D100" s="62"/>
+      <c r="E100" s="62"/>
+      <c r="F100" s="63">
+        <v>649484.196</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="B101" s="55"/>
+      <c r="C101" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="D101" s="56"/>
+      <c r="E101" s="56"/>
+      <c r="F101" s="60">
+        <v>4039.6661949275367</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="B102" s="52"/>
+      <c r="C102" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="D102" s="53"/>
+      <c r="E102" s="53"/>
+      <c r="F102" s="59">
+        <v>21061.172297826088</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="55" t="s">
+        <v>157</v>
+      </c>
+      <c r="B103" s="55"/>
+      <c r="C103" s="56" t="s">
+        <v>158</v>
+      </c>
+      <c r="D103" s="56"/>
+      <c r="E103" s="56"/>
+      <c r="F103" s="60">
+        <v>109816.16840579711</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="B104" s="52"/>
+      <c r="C104" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="D104" s="53"/>
+      <c r="E104" s="53"/>
+      <c r="F104" s="59">
+        <v>130877.3407036232</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="B105" s="55"/>
+      <c r="C105" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="D105" s="56"/>
+      <c r="E105" s="56"/>
+      <c r="F105" s="60">
+        <v>26916.53953850725</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="61" t="s">
+        <v>163</v>
+      </c>
+      <c r="B106" s="61"/>
+      <c r="C106" s="62" t="s">
+        <v>164</v>
+      </c>
+      <c r="D106" s="62"/>
+      <c r="E106" s="62"/>
+      <c r="F106" s="63">
+        <v>811317.742437058</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="61" t="s">
+        <v>165</v>
+      </c>
+      <c r="B107" s="61"/>
+      <c r="C107" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="D107" s="62"/>
+      <c r="E107" s="62"/>
+      <c r="F107" s="63">
+        <v>680440.4017334348</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B109" s="11"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="11"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="B110" s="50"/>
+      <c r="C110" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="D110" s="51"/>
+      <c r="E110" s="51"/>
+      <c r="F110" s="51"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="B111" s="50"/>
+      <c r="C111" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="D111" s="51"/>
+      <c r="E111" s="51"/>
+      <c r="F111" s="51"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="B112" s="50"/>
+      <c r="C112" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="D112" s="51"/>
+      <c r="E112" s="51"/>
+      <c r="F112" s="51"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="B113" s="50"/>
+      <c r="C113" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="D113" s="51"/>
+      <c r="E113" s="51"/>
+      <c r="F113" s="51"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="B114" s="50"/>
+      <c r="C114" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="D114" s="51"/>
+      <c r="E114" s="51"/>
+      <c r="F114" s="51"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="B115" s="50"/>
+      <c r="C115" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="D115" s="51"/>
+      <c r="E115" s="51"/>
+      <c r="F115" s="51"/>
+    </row>
+    <row r="117" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="B117" s="48"/>
+      <c r="C117" s="48"/>
+      <c r="D117" s="48"/>
+      <c r="E117" s="48"/>
+      <c r="F117" s="48"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="B118" s="49"/>
+      <c r="C118" s="49"/>
+      <c r="D118" s="49"/>
+      <c r="E118" s="49"/>
+      <c r="F118" s="49"/>
+    </row>
+    <row r="120" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="B120" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C120" s="66" t="s">
+        <v>182</v>
+      </c>
+      <c r="D120" s="66"/>
+      <c r="E120" s="66"/>
+      <c r="F120" s="67">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="B121" s="69">
+        <v>130</v>
+      </c>
+      <c r="C121" s="66" t="s">
+        <v>184</v>
+      </c>
+      <c r="D121" s="66"/>
+      <c r="E121" s="66"/>
+      <c r="F121" s="67">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="122" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="B122" s="69">
+        <v>45</v>
+      </c>
+      <c r="C122" s="66" t="s">
+        <v>186</v>
+      </c>
+      <c r="D122" s="66"/>
+      <c r="E122" s="66"/>
+      <c r="F122" s="67">
         <v>90</v>
       </c>
-      <c r="D67" s="46"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="B68" s="45"/>
-      <c r="C68" s="46" t="s">
+    </row>
+    <row r="123" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="64" t="s">
+        <v>187</v>
+      </c>
+      <c r="B123" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C123" s="66" t="s">
+        <v>188</v>
+      </c>
+      <c r="D123" s="66"/>
+      <c r="E123" s="66"/>
+      <c r="F123" s="67">
+        <v>207.28</v>
+      </c>
+    </row>
+    <row r="124" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B124" s="70" t="s">
+        <v>190</v>
+      </c>
+      <c r="C124" s="66" t="s">
+        <v>191</v>
+      </c>
+      <c r="D124" s="66"/>
+      <c r="E124" s="66"/>
+      <c r="F124" s="67">
+        <v>40.14</v>
+      </c>
+    </row>
+    <row r="125" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="B125" s="70" t="s">
+        <v>193</v>
+      </c>
+      <c r="C125" s="66" t="s">
+        <v>194</v>
+      </c>
+      <c r="D125" s="66"/>
+      <c r="E125" s="66"/>
+      <c r="F125" s="67">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="126" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="68" t="s">
+        <v>195</v>
+      </c>
+      <c r="B126" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="C126" s="66" t="s">
+        <v>197</v>
+      </c>
+      <c r="D126" s="66"/>
+      <c r="E126" s="66"/>
+      <c r="F126" s="67">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="127" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="B127" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C127" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="D127" s="66"/>
+      <c r="E127" s="66"/>
+      <c r="F127" s="67">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="128" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="B128" s="69">
+        <v>0</v>
+      </c>
+      <c r="C128" s="66" t="s">
+        <v>201</v>
+      </c>
+      <c r="D128" s="66"/>
+      <c r="E128" s="66"/>
+      <c r="F128" s="67">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="129" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="B129" s="69">
+        <v>500</v>
+      </c>
+      <c r="C129" s="66" t="s">
+        <v>203</v>
+      </c>
+      <c r="D129" s="66"/>
+      <c r="E129" s="66"/>
+      <c r="F129" s="67">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="130" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="B130" s="69">
+        <v>550</v>
+      </c>
+      <c r="C130" s="66" t="s">
+        <v>205</v>
+      </c>
+      <c r="D130" s="66"/>
+      <c r="E130" s="66"/>
+      <c r="F130" s="67">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="131" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="68" t="s">
+        <v>206</v>
+      </c>
+      <c r="B131" s="69">
+        <v>600</v>
+      </c>
+      <c r="C131" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="D131" s="66"/>
+      <c r="E131" s="66"/>
+      <c r="F131" s="67">
+        <v>97.12</v>
+      </c>
+    </row>
+    <row r="132" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="B132" s="69">
+        <v>650</v>
+      </c>
+      <c r="C132" s="66" t="s">
+        <v>209</v>
+      </c>
+      <c r="D132" s="66"/>
+      <c r="E132" s="66"/>
+      <c r="F132" s="67">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="133" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="68" t="s">
+        <v>210</v>
+      </c>
+      <c r="B133" s="69">
+        <v>700</v>
+      </c>
+      <c r="C133" s="66" t="s">
+        <v>211</v>
+      </c>
+      <c r="D133" s="66"/>
+      <c r="E133" s="66"/>
+      <c r="F133" s="67">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="134" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="68" t="s">
+        <v>212</v>
+      </c>
+      <c r="B134" s="69">
+        <v>750</v>
+      </c>
+      <c r="C134" s="66" t="s">
+        <v>213</v>
+      </c>
+      <c r="D134" s="66"/>
+      <c r="E134" s="66"/>
+      <c r="F134" s="67">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="135" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="B135" s="69">
+        <v>800</v>
+      </c>
+      <c r="C135" s="66" t="s">
+        <v>215</v>
+      </c>
+      <c r="D135" s="66"/>
+      <c r="E135" s="66"/>
+      <c r="F135" s="67">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="136" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="B136" s="69">
+        <v>850</v>
+      </c>
+      <c r="C136" s="66" t="s">
+        <v>217</v>
+      </c>
+      <c r="D136" s="66"/>
+      <c r="E136" s="66"/>
+      <c r="F136" s="67">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="137" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="B137" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C137" s="66" t="s">
+        <v>219</v>
+      </c>
+      <c r="D137" s="66"/>
+      <c r="E137" s="66"/>
+      <c r="F137" s="67">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="138" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="B138" s="69">
+        <v>1170</v>
+      </c>
+      <c r="C138" s="66" t="s">
+        <v>221</v>
+      </c>
+      <c r="D138" s="66"/>
+      <c r="E138" s="66"/>
+      <c r="F138" s="67">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="139" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="68" t="s">
+        <v>222</v>
+      </c>
+      <c r="B139" s="69">
+        <v>1560</v>
+      </c>
+      <c r="C139" s="66" t="s">
+        <v>223</v>
+      </c>
+      <c r="D139" s="66"/>
+      <c r="E139" s="66"/>
+      <c r="F139" s="67">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="140" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="B140" s="69">
+        <v>1820</v>
+      </c>
+      <c r="C140" s="66" t="s">
+        <v>225</v>
+      </c>
+      <c r="D140" s="66"/>
+      <c r="E140" s="66"/>
+      <c r="F140" s="67">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="141" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="B141" s="69">
+        <v>3110</v>
+      </c>
+      <c r="C141" s="66" t="s">
+        <v>227</v>
+      </c>
+      <c r="D141" s="66"/>
+      <c r="E141" s="66"/>
+      <c r="F141" s="67">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="142" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="68" t="s">
+        <v>228</v>
+      </c>
+      <c r="B142" s="69">
+        <v>2340</v>
+      </c>
+      <c r="C142" s="66" t="s">
+        <v>229</v>
+      </c>
+      <c r="D142" s="66"/>
+      <c r="E142" s="66"/>
+      <c r="F142" s="67">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="143" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="68" t="s">
+        <v>230</v>
+      </c>
+      <c r="B143" s="69">
+        <v>10</v>
+      </c>
+      <c r="C143" s="66" t="s">
+        <v>231</v>
+      </c>
+      <c r="D143" s="66"/>
+      <c r="E143" s="66"/>
+      <c r="F143" s="67">
         <v>92</v>
       </c>
-      <c r="D68" s="46"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="46"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="B69" s="45"/>
-      <c r="C69" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="D69" s="46"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="46"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="B70" s="45"/>
-      <c r="C70" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="B71" s="45"/>
-      <c r="C71" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="D71" s="46"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="B72" s="45"/>
-      <c r="C72" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
-      <c r="F72" s="46"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="B73" s="45"/>
-      <c r="C73" s="46" t="s">
-        <v>102</v>
-      </c>
-      <c r="D73" s="46"/>
-      <c r="E73" s="46"/>
-      <c r="F73" s="46"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="B74" s="45"/>
-      <c r="C74" s="46" t="s">
-        <v>48</v>
-      </c>
-      <c r="D74" s="46"/>
-      <c r="E74" s="46"/>
-      <c r="F74" s="46"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="B75" s="45"/>
-      <c r="C75" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="B76" s="45"/>
-      <c r="C76" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="B77" s="45"/>
-      <c r="C77" s="46" t="s">
-        <v>108</v>
-      </c>
-      <c r="D77" s="46"/>
-      <c r="E77" s="46"/>
-      <c r="F77" s="46"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="B78" s="45"/>
-      <c r="C78" s="46" t="s">
-        <v>110</v>
-      </c>
-      <c r="D78" s="46"/>
-      <c r="E78" s="46"/>
-      <c r="F78" s="46"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="B79" s="45"/>
-      <c r="C79" s="46" t="s">
+    </row>
+    <row r="144" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="68" t="s">
+        <v>232</v>
+      </c>
+      <c r="B144" s="69">
+        <v>20</v>
+      </c>
+      <c r="C144" s="66" t="s">
+        <v>233</v>
+      </c>
+      <c r="D144" s="66"/>
+      <c r="E144" s="66"/>
+      <c r="F144" s="67">
         <v>112</v>
       </c>
-      <c r="D79" s="46"/>
-      <c r="E79" s="46"/>
-      <c r="F79" s="46"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="45" t="s">
-        <v>113</v>
-      </c>
-      <c r="B80" s="45"/>
-      <c r="C80" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="D80" s="46"/>
-      <c r="E80" s="46"/>
-      <c r="F80" s="46"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="B81" s="45"/>
-      <c r="C81" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="D81" s="46"/>
-      <c r="E81" s="46"/>
-      <c r="F81" s="46"/>
-    </row>
-    <row r="83" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B83" s="11"/>
-      <c r="C83" s="11"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-    </row>
-    <row r="84" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="B85" s="47"/>
-      <c r="C85" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="D85" s="48"/>
-      <c r="E85" s="48"/>
-      <c r="F85" s="49">
-        <v>93.4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="B86" s="50"/>
-      <c r="C86" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="D86" s="51"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="B87" s="47"/>
-      <c r="C87" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="49">
-        <v>44.540800000000004</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="B88" s="50"/>
-      <c r="C88" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="52">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="B89" s="47"/>
-      <c r="C89" s="48" t="s">
-        <v>129</v>
-      </c>
-      <c r="D89" s="48"/>
-      <c r="E89" s="48"/>
-      <c r="F89" s="53">
-        <v>8980</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="B90" s="50"/>
-      <c r="C90" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="D90" s="51"/>
-      <c r="E90" s="51"/>
-      <c r="F90" s="52">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="47" t="s">
-        <v>132</v>
-      </c>
-      <c r="B91" s="47"/>
-      <c r="C91" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="D91" s="48"/>
-      <c r="E91" s="48"/>
-      <c r="F91" s="54">
-        <v>541033.14</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="B92" s="50"/>
-      <c r="C92" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="D92" s="51"/>
-      <c r="E92" s="51"/>
-      <c r="F92" s="55">
-        <v>10147.4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="47" t="s">
-        <v>136</v>
-      </c>
-      <c r="B93" s="47"/>
-      <c r="C93" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D93" s="48"/>
-      <c r="E93" s="48"/>
-      <c r="F93" s="54">
-        <v>18720</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="50" t="s">
-        <v>55</v>
-      </c>
-      <c r="B94" s="50"/>
-      <c r="C94" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="D94" s="51"/>
-      <c r="E94" s="51"/>
-      <c r="F94" s="55">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="47" t="s">
-        <v>139</v>
-      </c>
-      <c r="B95" s="47"/>
-      <c r="C95" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="D95" s="48"/>
-      <c r="E95" s="48"/>
-      <c r="F95" s="54">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="B96" s="50"/>
-      <c r="C96" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="D96" s="51"/>
-      <c r="E96" s="51"/>
-      <c r="F96" s="55">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="47" t="s">
-        <v>143</v>
-      </c>
-      <c r="B97" s="47"/>
-      <c r="C97" s="48" t="s">
-        <v>144</v>
-      </c>
-      <c r="D97" s="48"/>
-      <c r="E97" s="48"/>
-      <c r="F97" s="54">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="B98" s="50"/>
-      <c r="C98" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="D98" s="51"/>
-      <c r="E98" s="51"/>
-      <c r="F98" s="55">
-        <v>16216.320000000002</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="B99" s="47"/>
-      <c r="C99" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="D99" s="48"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="54">
-        <v>37360</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="B100" s="50"/>
-      <c r="C100" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="55">
-        <v>6207.336000000001</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="B101" s="56"/>
-      <c r="C101" s="57" t="s">
-        <v>151</v>
-      </c>
-      <c r="D101" s="57"/>
-      <c r="E101" s="57"/>
-      <c r="F101" s="58">
-        <v>649484.196</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="B102" s="50"/>
-      <c r="C102" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="D102" s="51"/>
-      <c r="E102" s="51"/>
-      <c r="F102" s="55">
-        <v>4039.6661949275367</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="47" t="s">
-        <v>154</v>
-      </c>
-      <c r="B103" s="47"/>
-      <c r="C103" s="48" t="s">
-        <v>155</v>
-      </c>
-      <c r="D103" s="48"/>
-      <c r="E103" s="48"/>
-      <c r="F103" s="54">
-        <v>21061.172297826088</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="B104" s="50"/>
-      <c r="C104" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="D104" s="51"/>
-      <c r="E104" s="51"/>
-      <c r="F104" s="55">
-        <v>109816.16840579711</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="B105" s="47"/>
-      <c r="C105" s="48" t="s">
-        <v>159</v>
-      </c>
-      <c r="D105" s="48"/>
-      <c r="E105" s="48"/>
-      <c r="F105" s="54">
-        <v>130877.3407036232</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="50" t="s">
-        <v>160</v>
-      </c>
-      <c r="B106" s="50"/>
-      <c r="C106" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="D106" s="51"/>
-      <c r="E106" s="51"/>
-      <c r="F106" s="55">
-        <v>26916.53953850725</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="56" t="s">
-        <v>162</v>
-      </c>
-      <c r="B107" s="56"/>
-      <c r="C107" s="57" t="s">
-        <v>163</v>
-      </c>
-      <c r="D107" s="57"/>
-      <c r="E107" s="57"/>
-      <c r="F107" s="58">
-        <v>811317.742437058</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="56" t="s">
-        <v>164</v>
-      </c>
-      <c r="B108" s="56"/>
-      <c r="C108" s="57" t="s">
-        <v>165</v>
-      </c>
-      <c r="D108" s="57"/>
-      <c r="E108" s="57"/>
-      <c r="F108" s="58">
-        <v>680440.4017334348</v>
-      </c>
-    </row>
-    <row r="110" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B110" s="11"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="11"/>
-      <c r="E110" s="11"/>
-      <c r="F110" s="11"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="B111" s="45"/>
-      <c r="C111" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="D111" s="46"/>
-      <c r="E111" s="46"/>
-      <c r="F111" s="46"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="B112" s="45"/>
-      <c r="C112" s="46" t="s">
+    </row>
+    <row r="145" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="64" t="s">
+        <v>234</v>
+      </c>
+      <c r="B145" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C145" s="66" t="s">
+        <v>235</v>
+      </c>
+      <c r="D145" s="66"/>
+      <c r="E145" s="66"/>
+      <c r="F145" s="67">
         <v>170</v>
       </c>
-      <c r="D112" s="46"/>
-      <c r="E112" s="46"/>
-      <c r="F112" s="46"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="B113" s="45"/>
-      <c r="C113" s="46" t="s">
-        <v>172</v>
-      </c>
-      <c r="D113" s="46"/>
-      <c r="E113" s="46"/>
-      <c r="F113" s="46"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="B114" s="45"/>
-      <c r="C114" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="D114" s="46"/>
-      <c r="E114" s="46"/>
-      <c r="F114" s="46"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="B115" s="45"/>
-      <c r="C115" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="D115" s="46"/>
-      <c r="E115" s="46"/>
-      <c r="F115" s="46"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="45" t="s">
-        <v>177</v>
-      </c>
-      <c r="B116" s="45"/>
-      <c r="C116" s="46" t="s">
-        <v>178</v>
-      </c>
-      <c r="D116" s="46"/>
-      <c r="E116" s="46"/>
-      <c r="F116" s="46"/>
-    </row>
-    <row r="118" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="B118" s="43"/>
-      <c r="C118" s="43"/>
-      <c r="D118" s="43"/>
-      <c r="E118" s="43"/>
-      <c r="F118" s="43"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="B119" s="44"/>
-      <c r="C119" s="44"/>
-      <c r="D119" s="44"/>
-      <c r="E119" s="44"/>
-      <c r="F119" s="44"/>
-    </row>
-    <row r="121" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="59" t="s">
-        <v>54</v>
-      </c>
-      <c r="B121" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C121" s="61" t="s">
-        <v>181</v>
-      </c>
-      <c r="D121" s="61"/>
-      <c r="E121" s="61"/>
-      <c r="F121" s="62">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="63" t="s">
-        <v>182</v>
-      </c>
-      <c r="B122" s="64">
-        <v>130</v>
-      </c>
-      <c r="C122" s="61" t="s">
-        <v>183</v>
-      </c>
-      <c r="D122" s="61"/>
-      <c r="E122" s="61"/>
-      <c r="F122" s="62">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="123" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="63" t="s">
-        <v>184</v>
-      </c>
-      <c r="B123" s="64">
+    </row>
+    <row r="146" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="68" t="s">
+        <v>236</v>
+      </c>
+      <c r="B146" s="69">
         <v>45</v>
       </c>
-      <c r="C123" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="D123" s="61"/>
-      <c r="E123" s="61"/>
-      <c r="F123" s="62">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="124" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="59" t="s">
-        <v>186</v>
-      </c>
-      <c r="B124" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C124" s="61" t="s">
-        <v>187</v>
-      </c>
-      <c r="D124" s="61"/>
-      <c r="E124" s="61"/>
-      <c r="F124" s="62">
-        <v>207.28</v>
-      </c>
-    </row>
-    <row r="125" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="63" t="s">
-        <v>188</v>
-      </c>
-      <c r="B125" s="65" t="s">
-        <v>189</v>
-      </c>
-      <c r="C125" s="61" t="s">
-        <v>190</v>
-      </c>
-      <c r="D125" s="61"/>
-      <c r="E125" s="61"/>
-      <c r="F125" s="62">
-        <v>40.14</v>
-      </c>
-    </row>
-    <row r="126" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="63" t="s">
-        <v>191</v>
-      </c>
-      <c r="B126" s="65" t="s">
-        <v>192</v>
-      </c>
-      <c r="C126" s="61" t="s">
-        <v>193</v>
-      </c>
-      <c r="D126" s="61"/>
-      <c r="E126" s="61"/>
-      <c r="F126" s="62">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="127" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="63" t="s">
-        <v>194</v>
-      </c>
-      <c r="B127" s="65" t="s">
-        <v>195</v>
-      </c>
-      <c r="C127" s="61" t="s">
-        <v>196</v>
-      </c>
-      <c r="D127" s="61"/>
-      <c r="E127" s="61"/>
-      <c r="F127" s="62">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="128" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="B128" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C128" s="61" t="s">
-        <v>198</v>
-      </c>
-      <c r="D128" s="61"/>
-      <c r="E128" s="61"/>
-      <c r="F128" s="62">
-        <v>10.95</v>
-      </c>
-    </row>
-    <row r="129" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="63" t="s">
-        <v>199</v>
-      </c>
-      <c r="B129" s="64">
-        <v>0</v>
-      </c>
-      <c r="C129" s="61" t="s">
-        <v>200</v>
-      </c>
-      <c r="D129" s="61"/>
-      <c r="E129" s="61"/>
-      <c r="F129" s="62">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="130" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="63" t="s">
-        <v>201</v>
-      </c>
-      <c r="B130" s="64">
-        <v>500</v>
-      </c>
-      <c r="C130" s="61" t="s">
-        <v>202</v>
-      </c>
-      <c r="D130" s="61"/>
-      <c r="E130" s="61"/>
-      <c r="F130" s="62">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="131" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="63" t="s">
-        <v>203</v>
-      </c>
-      <c r="B131" s="64">
-        <v>550</v>
-      </c>
-      <c r="C131" s="61" t="s">
-        <v>204</v>
-      </c>
-      <c r="D131" s="61"/>
-      <c r="E131" s="61"/>
-      <c r="F131" s="62">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="132" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="63" t="s">
-        <v>205</v>
-      </c>
-      <c r="B132" s="64">
-        <v>600</v>
-      </c>
-      <c r="C132" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="D132" s="61"/>
-      <c r="E132" s="61"/>
-      <c r="F132" s="62">
-        <v>97.12</v>
-      </c>
-    </row>
-    <row r="133" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="63" t="s">
-        <v>207</v>
-      </c>
-      <c r="B133" s="64">
-        <v>650</v>
-      </c>
-      <c r="C133" s="61" t="s">
-        <v>208</v>
-      </c>
-      <c r="D133" s="61"/>
-      <c r="E133" s="61"/>
-      <c r="F133" s="62">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="134" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="63" t="s">
-        <v>209</v>
-      </c>
-      <c r="B134" s="64">
-        <v>700</v>
-      </c>
-      <c r="C134" s="61" t="s">
-        <v>210</v>
-      </c>
-      <c r="D134" s="61"/>
-      <c r="E134" s="61"/>
-      <c r="F134" s="62">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="135" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="63" t="s">
-        <v>211</v>
-      </c>
-      <c r="B135" s="64">
-        <v>750</v>
-      </c>
-      <c r="C135" s="61" t="s">
-        <v>212</v>
-      </c>
-      <c r="D135" s="61"/>
-      <c r="E135" s="61"/>
-      <c r="F135" s="62">
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="136" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="63" t="s">
-        <v>213</v>
-      </c>
-      <c r="B136" s="64">
-        <v>800</v>
-      </c>
-      <c r="C136" s="61" t="s">
-        <v>214</v>
-      </c>
-      <c r="D136" s="61"/>
-      <c r="E136" s="61"/>
-      <c r="F136" s="62">
-        <v>8.08</v>
-      </c>
-    </row>
-    <row r="137" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="63" t="s">
-        <v>215</v>
-      </c>
-      <c r="B137" s="64">
-        <v>850</v>
-      </c>
-      <c r="C137" s="61" t="s">
-        <v>216</v>
-      </c>
-      <c r="D137" s="61"/>
-      <c r="E137" s="61"/>
-      <c r="F137" s="62">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="138" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="59" t="s">
-        <v>217</v>
-      </c>
-      <c r="B138" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C138" s="61" t="s">
-        <v>218</v>
-      </c>
-      <c r="D138" s="61"/>
-      <c r="E138" s="61"/>
-      <c r="F138" s="62">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="139" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="63" t="s">
-        <v>219</v>
-      </c>
-      <c r="B139" s="64">
-        <v>1170</v>
-      </c>
-      <c r="C139" s="61" t="s">
-        <v>220</v>
-      </c>
-      <c r="D139" s="61"/>
-      <c r="E139" s="61"/>
-      <c r="F139" s="62">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="140" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="63" t="s">
-        <v>221</v>
-      </c>
-      <c r="B140" s="64">
-        <v>1560</v>
-      </c>
-      <c r="C140" s="61" t="s">
-        <v>222</v>
-      </c>
-      <c r="D140" s="61"/>
-      <c r="E140" s="61"/>
-      <c r="F140" s="62">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="141" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="63" t="s">
-        <v>223</v>
-      </c>
-      <c r="B141" s="64">
-        <v>1820</v>
-      </c>
-      <c r="C141" s="61" t="s">
-        <v>224</v>
-      </c>
-      <c r="D141" s="61"/>
-      <c r="E141" s="61"/>
-      <c r="F141" s="62">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="142" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="63" t="s">
-        <v>225</v>
-      </c>
-      <c r="B142" s="64">
-        <v>3110</v>
-      </c>
-      <c r="C142" s="61" t="s">
-        <v>226</v>
-      </c>
-      <c r="D142" s="61"/>
-      <c r="E142" s="61"/>
-      <c r="F142" s="62">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="143" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="63" t="s">
-        <v>227</v>
-      </c>
-      <c r="B143" s="64">
-        <v>2340</v>
-      </c>
-      <c r="C143" s="61" t="s">
-        <v>228</v>
-      </c>
-      <c r="D143" s="61"/>
-      <c r="E143" s="61"/>
-      <c r="F143" s="62">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="144" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="63" t="s">
-        <v>229</v>
-      </c>
-      <c r="B144" s="64">
-        <v>10</v>
-      </c>
-      <c r="C144" s="61" t="s">
-        <v>230</v>
-      </c>
-      <c r="D144" s="61"/>
-      <c r="E144" s="61"/>
-      <c r="F144" s="62">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="145" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="63" t="s">
-        <v>231</v>
-      </c>
-      <c r="B145" s="64">
-        <v>20</v>
-      </c>
-      <c r="C145" s="61" t="s">
-        <v>232</v>
-      </c>
-      <c r="D145" s="61"/>
-      <c r="E145" s="61"/>
-      <c r="F145" s="62">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="146" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="59" t="s">
-        <v>233</v>
-      </c>
-      <c r="B146" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C146" s="61" t="s">
-        <v>234</v>
-      </c>
-      <c r="D146" s="61"/>
-      <c r="E146" s="61"/>
-      <c r="F146" s="62">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="147" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="63" t="s">
-        <v>235</v>
-      </c>
-      <c r="B147" s="64">
-        <v>45</v>
-      </c>
-      <c r="C147" t="s">
-        <v>48</v>
-      </c>
-      <c r="D147"/>
-      <c r="E147"/>
-      <c r="F147" t="s">
-        <v>48</v>
+      <c r="C146" t="s">
+        <v>50</v>
+      </c>
+      <c r="D146"/>
+      <c r="E146"/>
+      <c r="F146" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="198">
+  <mergeCells count="195">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -3405,9 +3467,9 @@
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D26:E26"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D27:E27"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="A29:C29"/>
@@ -3417,9 +3479,9 @@
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D32:E32"/>
     <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D33:E33"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="D34:F34"/>
     <mergeCell ref="A35:C35"/>
@@ -3428,31 +3490,30 @@
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="D37:F37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="E42:F42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A57:F57"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C61:F61"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="C62:F62"/>
     <mergeCell ref="A63:B63"/>
@@ -3491,9 +3552,9 @@
     <mergeCell ref="C79:F79"/>
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="C80:F80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:F81"/>
-    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:E83"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="C84:E84"/>
     <mergeCell ref="A85:B85"/>
@@ -3542,9 +3603,9 @@
     <mergeCell ref="C106:E106"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="C107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="C110:F110"/>
     <mergeCell ref="A111:B111"/>
     <mergeCell ref="C111:F111"/>
     <mergeCell ref="A112:B112"/>
@@ -3555,10 +3616,9 @@
     <mergeCell ref="C114:F114"/>
     <mergeCell ref="A115:B115"/>
     <mergeCell ref="C115:F115"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="C116:F116"/>
+    <mergeCell ref="A117:F117"/>
     <mergeCell ref="A118:F118"/>
-    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="C120:E120"/>
     <mergeCell ref="C121:E121"/>
     <mergeCell ref="C122:E122"/>
     <mergeCell ref="C123:E123"/>
@@ -3585,16 +3645,15 @@
     <mergeCell ref="C144:E144"/>
     <mergeCell ref="C145:E145"/>
     <mergeCell ref="C146:E146"/>
-    <mergeCell ref="C147:E147"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="78" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="82" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;8ul. Brzozowa 9, Poznań&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="57" max="16838" man="1"/>
-    <brk id="117" max="16838" man="1"/>
+    <brk id="56" max="16838" man="1"/>
+    <brk id="116" max="16838" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>